--- a/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital De Recreación Y Deporte.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital De Recreación Y Deporte.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="173">
   <si>
     <t>Entidad</t>
   </si>
@@ -429,7 +429,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -438,7 +438,7 @@
     <t>Programas de sensibilización sobre innovación pública., Espacios de ideación y cocreación con los equipos internos., Procesos de formación o capacitaciones en metodologías de innovación., Creación de equipos o laboratorios de innovación internos.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -3394,25 +3394,15 @@
         <v>66</v>
       </c>
       <c r="J24" s="10"/>
-      <c r="K24" s="8">
-        <v>4.0</v>
-      </c>
+      <c r="K24" s="8"/>
       <c r="L24" s="6"/>
-      <c r="M24" s="8">
-        <v>3.0</v>
-      </c>
+      <c r="M24" s="8"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="8">
-        <v>5.0</v>
-      </c>
+      <c r="O24" s="8"/>
       <c r="P24" s="6"/>
-      <c r="Q24" s="8">
-        <v>3.0</v>
-      </c>
+      <c r="Q24" s="8"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="S24" s="8"/>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
@@ -5745,7 +5735,7 @@
       <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>131</v>
       </c>
       <c r="E18" s="6"/>
@@ -5788,7 +5778,7 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>134</v>
       </c>
       <c r="E19" s="10"/>
